--- a/public/prices.xlsx
+++ b/public/prices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\la union\Desktop\fire_base_union\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96E21D17-EE4E-4FA0-93B7-72BED0DDE53A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16E74067-C279-49C4-8EFF-AA1695202E92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
